--- a/OUTPUT/direct_Q8F663_Leptospira_interrogans_serovar_Lai_str__56601.xlsx
+++ b/OUTPUT/direct_Q8F663_Leptospira_interrogans_serovar_Lai_str__56601.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
   </sheetData>
